--- a/example_excel_table_dataset_passport.xlsx
+++ b/example_excel_table_dataset_passport.xlsx
@@ -1,40 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Digital_Twin\Паспорт\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\python\create_dt_passport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF50EDB2-E603-4A1F-A15A-24FFCBB3F7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66986471-530D-4226-8136-52D658E0EE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1769EDFC-BF36-44D7-A506-F04B5D2062F5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="182">
   <si>
     <t>number</t>
   </si>
@@ -114,12 +106,6 @@
   </si>
   <si>
     <t>Частота обновляемости данных</t>
-  </si>
-  <si>
-    <t>Время обновления</t>
-  </si>
-  <si>
-    <t>Еженедельно по средам</t>
   </si>
   <si>
     <t>Общее наименование данных на русском</t>
@@ -210,13 +196,403 @@
   </si>
   <si>
     <t>Пример описания атрибута 2, км</t>
+  </si>
+  <si>
+    <t>По триггеру</t>
+  </si>
+  <si>
+    <t>Каждую минуту</t>
+  </si>
+  <si>
+    <t>Каждый час</t>
+  </si>
+  <si>
+    <t>Каждые 5 минут</t>
+  </si>
+  <si>
+    <t>Каждые 30 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С понедельника по пятницу в 03:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">В последний день месяца в 03:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждый час с 12:00 до 21:00 </t>
+  </si>
+  <si>
+    <t>Каждые 3 часа</t>
+  </si>
+  <si>
+    <t>С понедельника по пятницу каждый час</t>
+  </si>
+  <si>
+    <t>С понедельника по пятницу каждые 30 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 07:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в воскресенье в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в субботу в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждые 30 минут с 09:00 до 21:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">С 8:00 до 01:00 каждые 10 минут </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 03:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 9-го числа в 03:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в среду в 15:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально в первый четверг в 15:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в четверг в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально в первый вторник в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 01:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в пятницу в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в пятницу в 04:58 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в воскресенье в 18:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 21:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в пятницу в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 2-го числа в 04:58 </t>
+  </si>
+  <si>
+    <t>Каждый час в :05 минуту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 03:05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 03:00 </t>
+  </si>
+  <si>
+    <t>Каждые 15 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 17:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 01:15, 05:15, 09:15, 13:15, 17:15, 21:15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 18:00 </t>
+  </si>
+  <si>
+    <t>Каждые 2 часа в 15 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С понедельника по пятницу в 06:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 02:15, 06:15, 10:15, 14:15, 18:15, 22:15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно во вторник в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">С понедельника по пятницу в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в среду в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 19:00 </t>
+  </si>
+  <si>
+    <t>Каждые 40 минут</t>
+  </si>
+  <si>
+    <t>Каждые 10 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 06:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 17:30 </t>
+  </si>
+  <si>
+    <t>Каждый час в :03, :23, :43 минуту</t>
+  </si>
+  <si>
+    <t>Каждый час в :05, :25, :45 минуту</t>
+  </si>
+  <si>
+    <t>Каждый час в :02, :22, :42 минуту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 05:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 05:45 </t>
+  </si>
+  <si>
+    <t>Каждые 2 часа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально в первый четверг 12:05 </t>
+  </si>
+  <si>
+    <t>Каждые 2 часа 10 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-го числа месяца в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 03:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 03:10 </t>
+  </si>
+  <si>
+    <t>Каждые 20 минут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 03:15, 07:15, 11:15, 15:15, 19:15, 23:15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 03:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник каждый час 03:00-05:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в четверг в 13:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 15:00 </t>
+  </si>
+  <si>
+    <t>Ежемесячно 1-го числа в 15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 15:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 16:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в четверг в 16:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 18:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 21:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 21:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 05:00 </t>
+  </si>
+  <si>
+    <t>Каждый час 23:00-06:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждые 5 дней в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно в первый понедельник в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально в первую среду 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 25-го числа в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 5-го числа в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 01:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в пятницу в 02:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-го января в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 09:00 и 18:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-го января в 09:00, 21:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждый час 09:00-18:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник каждый час 09:00-18:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 08:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каждый час 09:00-20:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 10:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 11:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно в первый понедельник в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно в первый вторник в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально в первый четверг в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 02:22 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 03:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 04:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 03:33 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 03:33 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 04:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 03:44 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 04:44 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 04:44 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 04:44 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 00:05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 04:55 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник в 04:58 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 04:58 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в понедельник каждый час 09:00-21:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в пятницу в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно 1-го числа в 08:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально 1-го числа в 01:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">С понедельника по пятницу в 00:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Еженедельно в пятницу в 9:05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежедневно в 02:00 </t>
+  </si>
+  <si>
+    <t>Ежедневно в 09:00</t>
+  </si>
+  <si>
+    <t>Ежедневно в 10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С понедельника по пятницу в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежеквартально в первый понедельник в 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> !!! СТОЛБЦЫ И СТРОКИ НЕ МЕНЯТЬ (РЕДАКТИРОВАТЬ ТОЛЬКО ЗНАЧЕНИЯ ЯЧЕЕК), ИНАЧЕ БУДЕТ ОШИБКА ПРИ ЗАГРУЗКЕ !!!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,8 +681,32 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,8 +749,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -463,6 +869,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -496,15 +911,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -541,13 +950,19 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -944,117 +1359,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8601CD06-E7B6-4DF0-8E67-E68446FEFE0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Лист1"/>
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="40.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="53.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="21" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="21" t="s">
-        <v>36</v>
+      <c r="F1" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>42</v>
+      <c r="F3" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>31</v>
+      <c r="D4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>31</v>
+      <c r="D5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>26</v>
+      <c r="B6" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="10"/>
+    <row r="7" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:6" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1062,8 +1478,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:6" ht="46.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1107,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -1127,10 +1543,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>7</v>
@@ -1147,10 +1563,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>15</v>
@@ -1167,10 +1583,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>8</v>
@@ -1187,10 +1603,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>9</v>
@@ -1204,6 +1620,9 @@
     </row>
   </sheetData>
   <dataConsolidate/>
+  <mergeCells count="1">
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="B5">
     <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
@@ -1257,20 +1676,698 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:F16" xr:uid="{DD6595F2-FDB4-4293-880D-1B8C76250442}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:F16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{0E0853A7-E468-47F5-8C99-932671A2FF11}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Точка,Линия,Полигон"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12:D124" xr:uid="{7F071B5B-80A1-4C09-A308-844D2AEEDA7A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12:D124" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"string,integer,double,boolean,datetime"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E5" xr:uid="{6D447260-C87B-43CF-8529-D2C12657B24B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E5" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Да,Нет"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
+          <x14:formula1>
+            <xm:f>Лист2!$A$1:$A$130</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A130"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="46.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A130">
+    <sortCondition ref="A1:A130"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>